--- a/database_by_paper/Aucone_AUG_PPCF_2024_profile_database.xlsx
+++ b/database_by_paper/Aucone_AUG_PPCF_2024_profile_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\database_by_paper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9690D4F-31BF-4CDE-A6BB-579FA24178C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6074BCF3-F694-493E-B450-EE0E98EA9757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="396" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="396" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_PAPERS" sheetId="1" r:id="rId1"/>
